--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,16 +119,20 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
+    <t>人工智能产业指数</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>绝对收益率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>人工智能产业指数</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>单位：元</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -739,7 +743,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1054,6 +1058,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1063,7 +1070,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1377,6 +1384,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1420,7 +1430,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1735,6 +1745,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1744,7 +1757,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2055,6 +2068,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2098,7 +2114,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2413,6 +2429,9 @@
                 </c:pt>
                 <c:pt idx="104">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2422,7 +2441,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="105"/>
+                <c:ptCount val="106"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2736,6 +2755,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="104">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="105">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2758,11 +2780,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="474925312"/>
-        <c:axId val="486227968"/>
+        <c:axId val="107916672"/>
+        <c:axId val="543586560"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="474925312"/>
+        <c:axId val="107916672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2805,14 +2827,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="486227968"/>
+        <c:crossAx val="543586560"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="486227968"/>
+        <c:axId val="543586560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2861,7 +2883,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="474925312"/>
+        <c:crossAx val="107916672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3074,7 +3096,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3353,6 +3375,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3362,7 +3387,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3640,6 +3665,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3683,7 +3711,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3962,6 +3990,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3971,7 +4002,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4249,6 +4280,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4292,7 +4326,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4571,6 +4605,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4580,7 +4617,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4858,6 +4895,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4880,11 +4920,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="510284160"/>
-        <c:axId val="535826432"/>
+        <c:axId val="591592448"/>
+        <c:axId val="591610624"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="510284160"/>
+        <c:axId val="591592448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4927,14 +4967,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="535826432"/>
+        <c:crossAx val="591610624"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="535826432"/>
+        <c:axId val="591610624"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4983,7 +5023,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="510284160"/>
+        <c:crossAx val="591592448"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5196,7 +5236,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5475,6 +5515,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5484,7 +5527,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5762,6 +5805,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5805,7 +5851,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6084,6 +6130,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6093,7 +6142,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6371,6 +6420,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6414,7 +6466,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6693,6 +6745,9 @@
                 </c:pt>
                 <c:pt idx="92">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6702,7 +6757,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="93"/>
+                <c:ptCount val="94"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6980,6 +7035,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="93">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7002,11 +7060,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="571349632"/>
-        <c:axId val="600809856"/>
+        <c:axId val="667987328"/>
+        <c:axId val="669361664"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="571349632"/>
+        <c:axId val="667987328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7049,14 +7107,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="600809856"/>
+        <c:crossAx val="669361664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="600809856"/>
+        <c:axId val="669361664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7105,7 +7163,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571349632"/>
+        <c:crossAx val="667987328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7612,7 +7670,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF108"/>
+  <dimension ref="A1:AF109"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12059,7 +12117,7 @@
         <v>1.87002</v>
       </c>
       <c r="C108" s="20">
-        <v>1.1261140396413394</v>
+        <v>1.1257628092540124</v>
       </c>
       <c r="D108" s="21">
         <v>0</v>
@@ -12083,6 +12141,41 @@
         <v>259.19582720385745</v>
       </c>
       <c r="K108" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="12.75">
+      <c r="A109" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B109" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C109" s="20">
+        <v>1.1334752732368041</v>
+      </c>
+      <c r="D109" s="21">
+        <v>0</v>
+      </c>
+      <c r="E109" s="22">
+        <v>0</v>
+      </c>
+      <c r="F109" s="22">
+        <v>0</v>
+      </c>
+      <c r="G109" s="22">
+        <v>0</v>
+      </c>
+      <c r="H109" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I109" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J109" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K109" s="21">
         <v>795.53573587245569</v>
       </c>
     </row>
@@ -12104,7 +12197,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF96"/>
+  <dimension ref="A1:AF97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12142,10 +12235,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -12195,7 +12288,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -12262,7 +12355,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -16009,7 +16102,7 @@
         <v>1.87002</v>
       </c>
       <c r="C96" s="20">
-        <v>1.6436552000000013</v>
+        <v>1.6419015200000018</v>
       </c>
       <c r="D96" s="21">
         <v>0</v>
@@ -16033,6 +16126,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K96" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="12.75">
+      <c r="A97" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C97" s="20">
+        <v>1.6746592000000005</v>
+      </c>
+      <c r="D97" s="21">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22">
+        <v>0</v>
+      </c>
+      <c r="F97" s="22">
+        <v>0</v>
+      </c>
+      <c r="G97" s="22">
+        <v>0</v>
+      </c>
+      <c r="H97" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I97" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J97" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K97" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16054,7 +16182,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF96"/>
+  <dimension ref="A1:AF97"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16089,13 +16217,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16145,7 +16273,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -16212,7 +16340,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -19959,7 +20087,7 @@
         <v>1.87002</v>
       </c>
       <c r="C96" s="20">
-        <v>1.6436552000000013</v>
+        <v>1.6419015200000018</v>
       </c>
       <c r="D96" s="21">
         <v>0</v>
@@ -19983,6 +20111,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K96" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="12.75">
+      <c r="A97" s="15">
+        <v>46022</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1.87721</v>
+      </c>
+      <c r="C97" s="20">
+        <v>1.6746592000000005</v>
+      </c>
+      <c r="D97" s="21">
+        <v>0</v>
+      </c>
+      <c r="E97" s="22">
+        <v>0</v>
+      </c>
+      <c r="F97" s="22">
+        <v>0</v>
+      </c>
+      <c r="G97" s="22">
+        <v>0</v>
+      </c>
+      <c r="H97" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I97" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J97" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K97" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,20 +119,28 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
+    <t>MA250</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖金额</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>买卖份数</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>人工智能产业指数</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>MA250</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>绝对收益率</t>
+    <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -743,7 +751,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1061,6 +1069,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1070,7 +1081,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1387,6 +1398,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1430,7 +1444,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1748,6 +1762,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1757,7 +1774,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2071,6 +2088,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2114,7 +2134,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2432,6 +2452,9 @@
                 </c:pt>
                 <c:pt idx="105">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2441,7 +2464,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="106"/>
+                <c:ptCount val="107"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2758,6 +2781,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="105">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2780,11 +2806,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="107916672"/>
-        <c:axId val="543586560"/>
+        <c:axId val="530358656"/>
+        <c:axId val="530361344"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="107916672"/>
+        <c:axId val="530358656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2827,14 +2853,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="543586560"/>
+        <c:crossAx val="530361344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="543586560"/>
+        <c:axId val="530361344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2883,7 +2909,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="107916672"/>
+        <c:crossAx val="530358656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3096,7 +3122,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3378,6 +3404,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3387,7 +3416,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3668,6 +3697,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3711,7 +3743,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3993,6 +4025,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4002,7 +4037,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4283,6 +4318,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4326,7 +4364,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4608,6 +4646,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4617,7 +4658,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4898,6 +4939,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4920,11 +4964,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="591592448"/>
-        <c:axId val="591610624"/>
+        <c:axId val="556455040"/>
+        <c:axId val="556456576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="591592448"/>
+        <c:axId val="556455040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4967,14 +5011,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591610624"/>
+        <c:crossAx val="556456576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="591610624"/>
+        <c:axId val="556456576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5023,7 +5067,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="591592448"/>
+        <c:crossAx val="556455040"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5236,7 +5280,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5518,6 +5562,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5527,7 +5574,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5808,6 +5855,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5851,7 +5901,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6133,6 +6183,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6142,7 +6195,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6423,6 +6476,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6466,7 +6522,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6748,6 +6804,9 @@
                 </c:pt>
                 <c:pt idx="93">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6757,7 +6816,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="94"/>
+                <c:ptCount val="95"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7038,6 +7097,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="93">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7060,11 +7122,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="667987328"/>
-        <c:axId val="669361664"/>
+        <c:axId val="662116992"/>
+        <c:axId val="89461504"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="667987328"/>
+        <c:axId val="662116992"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7107,14 +7169,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="669361664"/>
+        <c:crossAx val="89461504"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="669361664"/>
+        <c:axId val="89461504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7163,7 +7225,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="667987328"/>
+        <c:crossAx val="662116992"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7271,7 +7333,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7314,7 +7376,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7357,7 +7419,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7670,7 +7732,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF109"/>
+  <dimension ref="A1:AF110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12179,6 +12241,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="110" spans="1:11" ht="12.75">
+      <c r="A110" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B110" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C110" s="20">
+        <v>1.1419948172142516</v>
+      </c>
+      <c r="D110" s="21">
+        <v>0</v>
+      </c>
+      <c r="E110" s="22">
+        <v>0</v>
+      </c>
+      <c r="F110" s="22">
+        <v>0</v>
+      </c>
+      <c r="G110" s="22">
+        <v>0</v>
+      </c>
+      <c r="H110" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I110" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J110" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K110" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12197,7 +12294,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF97"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12235,16 +12332,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="14" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>5</v>
@@ -12288,7 +12385,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -12355,7 +12452,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -16161,6 +16258,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K97" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="12.75">
+      <c r="A98" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B98" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C98" s="20">
+        <v>1.7296812799999999</v>
+      </c>
+      <c r="D98" s="21">
+        <v>0</v>
+      </c>
+      <c r="E98" s="22">
+        <v>0</v>
+      </c>
+      <c r="F98" s="22">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I98" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J98" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K98" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16182,7 +16314,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF97"/>
+  <dimension ref="A1:AF98"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16217,19 +16349,19 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>3</v>
-      </c>
       <c r="E1" s="14" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>5</v>
@@ -16273,7 +16405,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -16322,7 +16454,7 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="26" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>12</v>
@@ -16340,7 +16472,7 @@
         <v>16</v>
       </c>
       <c r="U4" s="11" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="V4" s="11" t="s">
         <v>18</v>
@@ -20146,6 +20278,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K97" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="12.75">
+      <c r="A98" s="15">
+        <v>46052</v>
+      </c>
+      <c r="B98" s="25">
+        <v>2.0358800000000001</v>
+      </c>
+      <c r="C98" s="20">
+        <v>1.7296812799999999</v>
+      </c>
+      <c r="D98" s="21">
+        <v>0</v>
+      </c>
+      <c r="E98" s="22">
+        <v>0</v>
+      </c>
+      <c r="F98" s="22">
+        <v>0</v>
+      </c>
+      <c r="G98" s="22">
+        <v>0</v>
+      </c>
+      <c r="H98" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I98" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J98" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K98" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="21">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -121,26 +121,6 @@
   <si>
     <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖金额</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>买卖份数</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>人工智能产业指数</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -751,7 +731,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1072,6 +1052,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1081,7 +1064,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1401,6 +1384,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1444,7 +1430,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1765,6 +1751,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1774,7 +1763,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2091,6 +2080,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2134,7 +2126,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2455,6 +2447,9 @@
                 </c:pt>
                 <c:pt idx="106">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2464,7 +2459,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="107"/>
+                <c:ptCount val="108"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2784,6 +2779,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="106">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="107">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2806,11 +2804,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="530358656"/>
-        <c:axId val="530361344"/>
+        <c:axId val="395304960"/>
+        <c:axId val="395306496"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="530358656"/>
+        <c:axId val="395304960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2853,14 +2851,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530361344"/>
+        <c:crossAx val="395306496"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="530361344"/>
+        <c:axId val="395306496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2909,7 +2907,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="530358656"/>
+        <c:crossAx val="395304960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3122,7 +3120,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3407,6 +3405,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3416,7 +3417,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3700,6 +3701,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3743,7 +3747,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4028,6 +4032,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4037,7 +4044,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4321,6 +4328,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4364,7 +4374,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4649,6 +4659,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4658,7 +4671,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4942,6 +4955,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4964,11 +4980,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="556455040"/>
-        <c:axId val="556456576"/>
+        <c:axId val="435932544"/>
+        <c:axId val="438347648"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="556455040"/>
+        <c:axId val="435932544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5011,14 +5027,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556456576"/>
+        <c:crossAx val="438347648"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="556456576"/>
+        <c:axId val="438347648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5067,7 +5083,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="556455040"/>
+        <c:crossAx val="435932544"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5280,7 +5296,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5565,6 +5581,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5574,7 +5593,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5858,6 +5877,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5901,7 +5923,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6186,6 +6208,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6195,7 +6220,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6479,6 +6504,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6522,7 +6550,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6807,6 +6835,9 @@
                 </c:pt>
                 <c:pt idx="94">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6816,7 +6847,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="95"/>
+                <c:ptCount val="96"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7100,6 +7131,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="94">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="95">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7122,11 +7156,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="662116992"/>
-        <c:axId val="89461504"/>
+        <c:axId val="525261824"/>
+        <c:axId val="526799616"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="662116992"/>
+        <c:axId val="525261824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7169,14 +7203,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89461504"/>
+        <c:crossAx val="526799616"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="89461504"/>
+        <c:axId val="526799616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7225,7 +7259,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="662116992"/>
+        <c:crossAx val="525261824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7333,7 +7367,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7376,7 +7410,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7419,7 +7453,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7732,7 +7766,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF110"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12276,6 +12310,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="111" spans="1:11" ht="12.75">
+      <c r="A111" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B111" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C111" s="20">
+        <v>1.1482512499999991</v>
+      </c>
+      <c r="D111" s="21">
+        <v>0</v>
+      </c>
+      <c r="E111" s="22">
+        <v>0</v>
+      </c>
+      <c r="F111" s="22">
+        <v>0</v>
+      </c>
+      <c r="G111" s="22">
+        <v>0</v>
+      </c>
+      <c r="H111" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I111" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J111" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K111" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12294,7 +12363,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AF99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12338,10 +12407,10 @@
         <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>5</v>
@@ -16293,6 +16362,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K98" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="12.75">
+      <c r="A99" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B99" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C99" s="20">
+        <v>1.7625963599999996</v>
+      </c>
+      <c r="D99" s="21">
+        <v>0</v>
+      </c>
+      <c r="E99" s="22">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22">
+        <v>0</v>
+      </c>
+      <c r="G99" s="22">
+        <v>0</v>
+      </c>
+      <c r="H99" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I99" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J99" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K99" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16314,7 +16418,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF98"/>
+  <dimension ref="A1:AF99"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16349,19 +16453,19 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>5</v>
@@ -16454,7 +16558,7 @@
       </c>
       <c r="L4" s="7"/>
       <c r="O4" s="26" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="P4" s="11" t="s">
         <v>12</v>
@@ -20313,6 +20417,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K98" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="12.75">
+      <c r="A99" s="15">
+        <v>46080</v>
+      </c>
+      <c r="B99" s="25">
+        <v>2.0871900000000001</v>
+      </c>
+      <c r="C99" s="20">
+        <v>1.7625963599999996</v>
+      </c>
+      <c r="D99" s="21">
+        <v>0</v>
+      </c>
+      <c r="E99" s="22">
+        <v>0</v>
+      </c>
+      <c r="F99" s="22">
+        <v>0</v>
+      </c>
+      <c r="G99" s="22">
+        <v>0</v>
+      </c>
+      <c r="H99" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I99" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J99" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K99" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,8 +119,20 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
+    <t>日期</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能产业指数</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>MA250</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>单位：元</t>
+    <phoneticPr fontId="17" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -731,7 +743,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1055,6 +1067,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1064,7 +1079,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1387,6 +1402,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1430,7 +1448,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1754,6 +1772,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1763,7 +1784,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2083,6 +2104,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2126,7 +2150,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2450,6 +2474,9 @@
                 </c:pt>
                 <c:pt idx="107">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2459,7 +2486,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="108"/>
+                <c:ptCount val="109"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2782,6 +2809,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="107">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="108">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2804,11 +2834,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="395304960"/>
-        <c:axId val="395306496"/>
+        <c:axId val="427480192"/>
+        <c:axId val="427482112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="395304960"/>
+        <c:axId val="427480192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2851,14 +2881,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395306496"/>
+        <c:crossAx val="427482112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="395306496"/>
+        <c:axId val="427482112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2907,7 +2937,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="395304960"/>
+        <c:crossAx val="427480192"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3120,7 +3150,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3408,6 +3438,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3417,7 +3450,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3704,6 +3737,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3747,7 +3783,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4035,6 +4071,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4044,7 +4083,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4331,6 +4370,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4374,7 +4416,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4662,6 +4704,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4671,7 +4716,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4958,6 +5003,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -4980,11 +5028,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="435932544"/>
-        <c:axId val="438347648"/>
+        <c:axId val="433566464"/>
+        <c:axId val="433568000"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="435932544"/>
+        <c:axId val="433566464"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5027,14 +5075,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="438347648"/>
+        <c:crossAx val="433568000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="438347648"/>
+        <c:axId val="433568000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5083,7 +5131,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="435932544"/>
+        <c:crossAx val="433566464"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5296,7 +5344,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5584,6 +5632,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5593,7 +5644,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5880,6 +5931,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5923,7 +5977,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6211,6 +6265,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6220,7 +6277,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6507,6 +6564,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6550,7 +6610,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6838,6 +6898,9 @@
                 </c:pt>
                 <c:pt idx="95">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6847,7 +6910,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="96"/>
+                <c:ptCount val="97"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7134,6 +7197,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="95">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="96">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7156,11 +7222,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="525261824"/>
-        <c:axId val="526799616"/>
+        <c:axId val="79880576"/>
+        <c:axId val="79882112"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="525261824"/>
+        <c:axId val="79880576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7203,14 +7269,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="526799616"/>
+        <c:crossAx val="79882112"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="526799616"/>
+        <c:axId val="79882112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7259,7 +7325,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="525261824"/>
+        <c:crossAx val="79880576"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7367,7 +7433,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7410,7 +7476,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7453,7 +7519,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7766,7 +7832,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF112"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12345,6 +12411,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="112" spans="1:11" ht="12.75">
+      <c r="A112" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B112" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C112" s="20">
+        <v>1.1561043221110083</v>
+      </c>
+      <c r="D112" s="21">
+        <v>0</v>
+      </c>
+      <c r="E112" s="22">
+        <v>0</v>
+      </c>
+      <c r="F112" s="22">
+        <v>0</v>
+      </c>
+      <c r="G112" s="22">
+        <v>0</v>
+      </c>
+      <c r="H112" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I112" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J112" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K112" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12363,7 +12464,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF99"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12398,13 +12499,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -12454,7 +12555,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -16397,6 +16498,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K99" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="12.75">
+      <c r="A100" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B100" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C100" s="20">
+        <v>1.7862818</v>
+      </c>
+      <c r="D100" s="21">
+        <v>0</v>
+      </c>
+      <c r="E100" s="22">
+        <v>0</v>
+      </c>
+      <c r="F100" s="22">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I100" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J100" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K100" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16418,7 +16554,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF99"/>
+  <dimension ref="A1:AF100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16453,13 +16589,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -20455,6 +20591,41 @@
         <v>380.47791488128132</v>
       </c>
     </row>
+    <row r="100" spans="1:11" ht="12.75">
+      <c r="A100" s="15">
+        <v>46112</v>
+      </c>
+      <c r="B100" s="25">
+        <v>1.8343499999999999</v>
+      </c>
+      <c r="C100" s="20">
+        <v>1.7862818</v>
+      </c>
+      <c r="D100" s="21">
+        <v>0</v>
+      </c>
+      <c r="E100" s="22">
+        <v>0</v>
+      </c>
+      <c r="F100" s="22">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22">
+        <v>0</v>
+      </c>
+      <c r="H100" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I100" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J100" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K100" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">

--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -117,6 +117,10 @@
   <si>
     <t>单位：元</t>
     <phoneticPr fontId="17" type="noConversion"/>
+  </si>
+  <si>
+    <t>MA250</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>日期</t>
@@ -743,7 +747,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1070,6 +1074,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1079,7 +1086,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1405,6 +1412,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1448,7 +1458,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1775,6 +1785,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1784,7 +1797,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2107,6 +2120,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2150,7 +2166,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2477,6 +2493,9 @@
                 </c:pt>
                 <c:pt idx="108">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2486,7 +2505,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="109"/>
+                <c:ptCount val="110"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2812,6 +2831,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="108">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="109">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2834,11 +2856,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="427480192"/>
-        <c:axId val="427482112"/>
+        <c:axId val="495759360"/>
+        <c:axId val="495760896"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="427480192"/>
+        <c:axId val="495759360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2881,14 +2903,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427482112"/>
+        <c:crossAx val="495760896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="427482112"/>
+        <c:axId val="495760896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2937,7 +2959,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="427480192"/>
+        <c:crossAx val="495759360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3150,7 +3172,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3441,6 +3463,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3450,7 +3475,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3740,6 +3765,9 @@
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>1179.2233563460313</c:v>
                 </c:pt>
               </c:numCache>
@@ -3783,7 +3811,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4074,6 +4102,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4083,7 +4114,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4373,6 +4404,9 @@
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>1725.4194238613065</c:v>
                 </c:pt>
               </c:numCache>
@@ -4416,7 +4450,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4707,6 +4741,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4716,7 +4753,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5006,6 +5043,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -5028,11 +5068,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="433566464"/>
-        <c:axId val="433568000"/>
+        <c:axId val="496231168"/>
+        <c:axId val="496232704"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="433566464"/>
+        <c:axId val="496231168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5075,14 +5115,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433568000"/>
+        <c:crossAx val="496232704"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="433568000"/>
+        <c:axId val="496232704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5131,7 +5171,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="433566464"/>
+        <c:crossAx val="496231168"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5344,7 +5384,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5635,6 +5675,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5644,7 +5687,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5934,6 +5977,9 @@
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>250.29467916284148</c:v>
                 </c:pt>
               </c:numCache>
@@ -5977,7 +6023,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6268,6 +6314,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6277,7 +6326,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6567,6 +6616,9 @@
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>380.47791488128132</c:v>
                 </c:pt>
               </c:numCache>
@@ -6610,7 +6662,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6901,6 +6953,9 @@
                 </c:pt>
                 <c:pt idx="96">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6910,7 +6965,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="97"/>
+                <c:ptCount val="98"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7200,6 +7255,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="96">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="97">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7222,11 +7280,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="79880576"/>
-        <c:axId val="79882112"/>
+        <c:axId val="509161856"/>
+        <c:axId val="509163392"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="79880576"/>
+        <c:axId val="509161856"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7269,14 +7327,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79882112"/>
+        <c:crossAx val="509163392"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="79882112"/>
+        <c:axId val="509163392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7325,7 +7383,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79880576"/>
+        <c:crossAx val="509161856"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7433,7 +7491,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7476,7 +7534,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7519,7 +7577,7 @@
         <xdr:cNvPr id="2" name="图表 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7832,7 +7890,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AF113"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12446,6 +12504,41 @@
         <v>795.53573587245569</v>
       </c>
     </row>
+    <row r="113" spans="1:11" ht="12.75">
+      <c r="A113" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B113" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C113" s="20">
+        <v>1.1626960820559045</v>
+      </c>
+      <c r="D113" s="21">
+        <v>0</v>
+      </c>
+      <c r="E113" s="22">
+        <v>0</v>
+      </c>
+      <c r="F113" s="22">
+        <v>0</v>
+      </c>
+      <c r="G113" s="22">
+        <v>0</v>
+      </c>
+      <c r="H113" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I113" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J113" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K113" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="G3">
@@ -12464,7 +12557,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12499,13 +12592,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>20</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -12555,7 +12648,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -16533,6 +16626,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K100" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="12.75">
+      <c r="A101" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B101" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C101" s="20">
+        <v>1.8123291999999998</v>
+      </c>
+      <c r="D101" s="21">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22">
+        <v>0</v>
+      </c>
+      <c r="G101" s="22">
+        <v>0</v>
+      </c>
+      <c r="H101" s="22">
+        <v>1179.2233563460313</v>
+      </c>
+      <c r="I101" s="22">
+        <v>1725.4194238613065</v>
+      </c>
+      <c r="J101" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K101" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16554,7 +16682,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF100"/>
+  <dimension ref="A1:AF101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16589,13 +16717,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16645,7 +16773,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -20623,6 +20751,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K100" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="12.75">
+      <c r="A101" s="15">
+        <v>46142</v>
+      </c>
+      <c r="B101" s="25">
+        <v>1.9266700000000001</v>
+      </c>
+      <c r="C101" s="20">
+        <v>1.8123291999999998</v>
+      </c>
+      <c r="D101" s="21">
+        <v>0</v>
+      </c>
+      <c r="E101" s="22">
+        <v>0</v>
+      </c>
+      <c r="F101" s="22">
+        <v>0</v>
+      </c>
+      <c r="G101" s="22">
+        <v>0</v>
+      </c>
+      <c r="H101" s="22">
+        <v>250.29467916284148</v>
+      </c>
+      <c r="I101" s="22">
+        <v>380.47791488128132</v>
+      </c>
+      <c r="J101" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K101" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>

--- a/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
+++ b/lai/valuationquan/AIindex/AIinduindexmodel4cn.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -119,10 +119,6 @@
     <phoneticPr fontId="17" type="noConversion"/>
   </si>
   <si>
-    <t>MA250</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>日期</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -135,8 +131,8 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>单位：元</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <t>MA250</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -747,7 +743,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1077,6 +1073,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1086,7 +1085,7 @@
               <c:f>'模型四 (1)平均线'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0.48968411061224032</c:v>
                 </c:pt>
@@ -1415,6 +1414,9 @@
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>536.33990866859824</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>536.33990866859824</c:v>
                 </c:pt>
               </c:numCache>
@@ -1458,7 +1460,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -1788,6 +1790,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1797,7 +1802,7 @@
               <c:f>'模型四 (1)平均线'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="1">
                   <c:v>0.48968411061224026</c:v>
                 </c:pt>
@@ -2123,6 +2128,9 @@
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>795.53573587245569</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>795.53573587245569</c:v>
                 </c:pt>
               </c:numCache>
@@ -2166,7 +2174,7 @@
               <c:f>'模型四 (1)平均线'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>42825</c:v>
                 </c:pt>
@@ -2496,6 +2504,9 @@
                 </c:pt>
                 <c:pt idx="109">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2505,7 +2516,7 @@
               <c:f>'模型四 (1)平均线'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="110"/>
+                <c:ptCount val="111"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2834,6 +2845,9 @@
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
                 <c:pt idx="109">
+                  <c:v>259.19582720385745</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>259.19582720385745</c:v>
                 </c:pt>
               </c:numCache>
@@ -2856,11 +2870,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="495759360"/>
-        <c:axId val="495760896"/>
+        <c:axId val="442372480"/>
+        <c:axId val="442374016"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="495759360"/>
+        <c:axId val="442372480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2903,14 +2917,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495760896"/>
+        <c:crossAx val="442374016"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="495760896"/>
+        <c:axId val="442374016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2959,7 +2973,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="495759360"/>
+        <c:crossAx val="442372480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3172,7 +3186,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -3466,6 +3480,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3475,7 +3492,7 @@
               <c:f>'模型四 (1)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -3769,6 +3786,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>1179.2233563460313</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1179.7195080910908</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3811,7 +3831,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4105,6 +4125,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4114,7 +4137,7 @@
               <c:f>'模型四 (1)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -4408,6 +4431,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>1725.4194238613065</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1725.915575606366</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4450,7 +4476,7 @@
               <c:f>'模型四 (1)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -4744,6 +4770,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4753,7 +4782,7 @@
               <c:f>'模型四 (1)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5046,6 +5075,9 @@
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
                 <c:pt idx="97">
+                  <c:v>546.19606751527522</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>546.19606751527522</c:v>
                 </c:pt>
               </c:numCache>
@@ -5068,11 +5100,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="496231168"/>
-        <c:axId val="496232704"/>
+        <c:axId val="450596224"/>
+        <c:axId val="450606208"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="496231168"/>
+        <c:axId val="450596224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5115,14 +5147,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="496232704"/>
+        <c:crossAx val="450606208"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="496232704"/>
+        <c:axId val="450606208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5171,7 +5203,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="496231168"/>
+        <c:crossAx val="450596224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5384,7 +5416,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -5678,6 +5710,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5687,7 +5722,7 @@
               <c:f>'模型四 (3)MA250'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -5981,6 +6016,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>250.29467916284148</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>250.30355595263484</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6023,7 +6061,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6317,6 +6355,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6326,7 +6367,7 @@
               <c:f>'模型四 (3)MA250'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -6620,6 +6661,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>380.47791488128132</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>380.48679167107468</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6662,7 +6706,7 @@
               <c:f>'模型四 (3)MA250'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>43189</c:v>
                 </c:pt>
@@ -6956,6 +7000,9 @@
                 </c:pt>
                 <c:pt idx="97">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6965,7 +7012,7 @@
               <c:f>'模型四 (3)MA250'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="98"/>
+                <c:ptCount val="99"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7258,6 +7305,9 @@
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
                 <c:pt idx="97">
+                  <c:v>130.18323571843985</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>130.18323571843985</c:v>
                 </c:pt>
               </c:numCache>
@@ -7280,11 +7330,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="509161856"/>
-        <c:axId val="509163392"/>
+        <c:axId val="451266432"/>
+        <c:axId val="472383488"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="509161856"/>
+        <c:axId val="451266432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7327,14 +7377,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="509163392"/>
+        <c:crossAx val="472383488"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="509163392"/>
+        <c:axId val="472383488"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7383,7 +7433,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="509161856"/>
+        <c:crossAx val="451266432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7890,7 +7940,7 @@
   <sheetPr codeName="Sheet1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:AF113"/>
+  <dimension ref="A1:AF114"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12442,7 +12492,7 @@
         <v>2.0871900000000001</v>
       </c>
       <c r="C111" s="20">
-        <v>1.1482512499999991</v>
+        <v>1.1478195540229874</v>
       </c>
       <c r="D111" s="21">
         <v>0</v>
@@ -12477,7 +12527,7 @@
         <v>1.8343499999999999</v>
       </c>
       <c r="C112" s="20">
-        <v>1.1561043221110083</v>
+        <v>1.1556805234410541</v>
       </c>
       <c r="D112" s="21">
         <v>0</v>
@@ -12536,6 +12586,41 @@
         <v>259.19582720385745</v>
       </c>
       <c r="K113" s="21">
+        <v>795.53573587245569</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="12.75">
+      <c r="A114" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B114" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C114" s="20">
+        <v>1.1691162343470469</v>
+      </c>
+      <c r="D114" s="21">
+        <v>0</v>
+      </c>
+      <c r="E114" s="22">
+        <v>0</v>
+      </c>
+      <c r="F114" s="22">
+        <v>0</v>
+      </c>
+      <c r="G114" s="22">
+        <v>0</v>
+      </c>
+      <c r="H114" s="22">
+        <v>536.33990866859824</v>
+      </c>
+      <c r="I114" s="22">
+        <v>795.53573587245569</v>
+      </c>
+      <c r="J114" s="22">
+        <v>259.19582720385745</v>
+      </c>
+      <c r="K114" s="21">
         <v>795.53573587245569</v>
       </c>
     </row>
@@ -12554,10 +12639,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:AF101"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:AF102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -12592,13 +12675,13 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>3</v>
@@ -16567,7 +16650,7 @@
         <v>2.0871900000000001</v>
       </c>
       <c r="C99" s="20">
-        <v>1.7625963599999996</v>
+        <v>1.7605544399999997</v>
       </c>
       <c r="D99" s="21">
         <v>0</v>
@@ -16602,7 +16685,7 @@
         <v>1.8343499999999999</v>
       </c>
       <c r="C100" s="20">
-        <v>1.7862818</v>
+        <v>1.7846445999999998</v>
       </c>
       <c r="D100" s="21">
         <v>0</v>
@@ -16637,7 +16720,7 @@
         <v>1.9266700000000001</v>
       </c>
       <c r="C101" s="20">
-        <v>1.8123291999999998</v>
+        <v>1.8182105999999996</v>
       </c>
       <c r="D101" s="21">
         <v>0</v>
@@ -16661,6 +16744,41 @@
         <v>546.19606751527522</v>
       </c>
       <c r="K101" s="21">
+        <v>1725.4194238613065</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="12.75">
+      <c r="A102" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B102" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C102" s="20">
+        <v>1.8510212799999999</v>
+      </c>
+      <c r="D102" s="21">
+        <v>0.49615174505950516</v>
+      </c>
+      <c r="E102" s="22">
+        <v>0.27065824303759423</v>
+      </c>
+      <c r="F102" s="22">
+        <v>0.27065824303759423</v>
+      </c>
+      <c r="G102" s="22">
+        <v>0.49615174505950516</v>
+      </c>
+      <c r="H102" s="22">
+        <v>1179.7195080910908</v>
+      </c>
+      <c r="I102" s="22">
+        <v>1725.915575606366</v>
+      </c>
+      <c r="J102" s="22">
+        <v>546.19606751527522</v>
+      </c>
+      <c r="K102" s="21">
         <v>1725.4194238613065</v>
       </c>
     </row>
@@ -16679,10 +16797,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet3">
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1:AF101"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:AF102"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16717,10 +16833,10 @@
   <sheetData>
     <row r="1" spans="1:32" s="12" customFormat="1" ht="27" customHeight="1">
       <c r="A1" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>23</v>
@@ -16773,7 +16889,7 @@
         <v>1550</v>
       </c>
       <c r="E3" s="28" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5">
@@ -20692,7 +20808,7 @@
         <v>2.0871900000000001</v>
       </c>
       <c r="C99" s="20">
-        <v>1.7625963599999996</v>
+        <v>1.7605544399999997</v>
       </c>
       <c r="D99" s="21">
         <v>0</v>
@@ -20727,7 +20843,7 @@
         <v>1.8343499999999999</v>
       </c>
       <c r="C100" s="20">
-        <v>1.7862818</v>
+        <v>1.7846445999999998</v>
       </c>
       <c r="D100" s="21">
         <v>0</v>
@@ -20762,7 +20878,7 @@
         <v>1.9266700000000001</v>
       </c>
       <c r="C101" s="20">
-        <v>1.8123291999999998</v>
+        <v>1.8182105999999996</v>
       </c>
       <c r="D101" s="21">
         <v>0</v>
@@ -20786,6 +20902,41 @@
         <v>130.18323571843985</v>
       </c>
       <c r="K101" s="21">
+        <v>380.47791488128132</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="12.75">
+      <c r="A102" s="15">
+        <v>46171</v>
+      </c>
+      <c r="B102" s="25">
+        <v>1.8331300000000001</v>
+      </c>
+      <c r="C102" s="20">
+        <v>1.8510212799999999</v>
+      </c>
+      <c r="D102" s="21">
+        <v>8.8767897933480899E-3</v>
+      </c>
+      <c r="E102" s="22">
+        <v>4.8424224104935765E-3</v>
+      </c>
+      <c r="F102" s="22">
+        <v>4.8424224104935765E-3</v>
+      </c>
+      <c r="G102" s="22">
+        <v>8.8767897933480899E-3</v>
+      </c>
+      <c r="H102" s="22">
+        <v>250.30355595263484</v>
+      </c>
+      <c r="I102" s="22">
+        <v>380.48679167107468</v>
+      </c>
+      <c r="J102" s="22">
+        <v>130.18323571843985</v>
+      </c>
+      <c r="K102" s="21">
         <v>380.47791488128132</v>
       </c>
     </row>
